--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/WASHINGTON_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/WASHINGTON_2012.xlsx
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C128">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C583">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C663">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C664">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C681">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C684">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1046">
